--- a/Hardware/RebotModel/BOM.xlsx
+++ b/Hardware/RebotModel/BOM.xlsx
@@ -1,33 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="30720" windowHeight="13380"/>
+    <workbookView windowWidth="25050" windowHeight="12150"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="69">
   <si>
     <t>Part Name</t>
   </si>
@@ -41,13 +28,16 @@
     <t>Quantity</t>
   </si>
   <si>
+    <t>Price($)</t>
+  </si>
+  <si>
     <t>Servo</t>
   </si>
   <si>
     <t>https://www.amazon.com/magnetic-rotating-minibus-steering-black/dp/B0BP645PF9/ref=sr_1_1?crid=3LS7GUSJS60AA&amp;dib=eyJ2IjoiMSJ9.BE-GIc9FaHnRL9psBoLbxkU7ijHDkcEJvYXOaj1mbmAj27dNP-TEUujrx4p-RL03jtV--AeEGoP12WrvAklEwZKhyBDgqntuxtMmb_GO01iH3JglqKW517CkrE9ZtYij_RSWb_cIH2xjQjYbKJBM7SO5kn-_RA3BKb2Ak5xWc3aLV8Fr-fiV-ZKwNqgSy3C0.xqcww89BSFNI306TRwVLMXFfjPNHTSw82tZBhYTCXo8&amp;dib_tag=se&amp;keywords=ST3032&amp;qid=1764674316&amp;sprefix=st3032%2Caps%2C351&amp;sr=8-1</t>
   </si>
   <si>
-    <t>ST3032</t>
+    <t>1pcs ST3032 all metal hollow cup 360 degree magnetic coding rotating TTL signal level minibus steering gear (black)</t>
   </si>
   <si>
     <t>Motor</t>
@@ -56,7 +46,7 @@
     <t>https://www.amazon.com/Fityle-Gimbal-Brushless-100-200g-Quadcopter/dp/B07JLSL8ZV/ref=sr_1_13?crid=24M2HR8C6IM58&amp;dib=eyJ2IjoiMSJ9.GD2eP8zLbh39g3qy2nAGsGbCBnbohYPT-8UpA_Z7iXVh91pQHkVDFBFsig_IEjEL3Sffd_ST1EdUJAcRiKS1tWHN-Gqw70BZx1US2EIKlJpQmmRUfnBFuL8ZQI_5S6WuusbsSHjlyBuc9rktqq9FOCtrWQt5PCX9QuhE0secsAo-37dyzI7amI25GrDXeQjwyn_Zb-m0PObfGWhbFPP86QegpBuUqFl7npJ002xeMBS5nUfW9Ka1CS4Vc9k92e92QQHodT7KgXjz-XbsqSQxAXFXZl0zMOIaXlC_79vJR5E.VX62aCxSFDlVT0HlIfVQERrn-j-P9X6Dk706DP-i7NI&amp;dib_tag=se&amp;keywords=2208+MOTOR&amp;qid=1764670475&amp;sprefix=2208+motor%2Caps%2C564&amp;sr=8-13</t>
   </si>
   <si>
-    <t>2208，&lt; 200kv</t>
+    <t>Fityle 2208 90KV 3mm Shaft Gimbal Brushless Motor for 100-200g Gopro3 RC Quadcopter</t>
   </si>
   <si>
     <t>Neodymium Magnet</t>
@@ -65,16 +55,16 @@
     <t>https://www.amazon.com/TRYMAG-Magnets-Neodymium-Whiteboard-Billboard/dp/B09SL2K4BP/ref=sr_1_1?crid=22JKHNBK7PALG&amp;dib=eyJ2IjoiMSJ9.RLPwftsKniozBWj0uh7U142P6RNz4Q4tko0qF8ScuD1UN5UrZjklVoqmEoHKCs1gy-7B-vu8epw-mLdBleLBRQGU204WQ8Mz3Hkj7LiBt81eNZGcRk9iyBYXrOE4EUTTKvJIZFlT2UKdOIuoPVPzuIVK3wZi3F99HscRW39_0PqbO2ftOCFCYt8y_iwUkWJjGeeyTl6dJpaGgIg5pfOES5M26rosCLV3ycoXuQuOVwU.ue-loQpwydrVQT2-in4isvL6W87LcpdknIpnYfFi5Yc&amp;dib_tag=se&amp;keywords=neodymium%2Bmagnet%2B4x1&amp;qid=1764670685&amp;sprefix=neodymium%2Bmagnet%2B4x%2Caps%2C413&amp;sr=8-1&amp;th=1</t>
   </si>
   <si>
-    <t>w4*h1</t>
+    <t>TRYMAG 340Pcs Small 4x1mm Mini Neodymium Magnets</t>
   </si>
   <si>
     <t>Battery</t>
   </si>
   <si>
-    <t>https://item.taobao.com/item.htm?id=559166020526&amp;mi_id=0000fFtHFvsNuZeTME9MVwduHvvvFWSfuFDbCS_zVGx7Vf0&amp;spm=tbpc.boughtlist.suborder_itempic.d559166020526.1b2a2e8damrYGA</t>
-  </si>
-  <si>
-    <t>1000mah</t>
+    <t>https://www.amazon.com/MakerHawk-Rechargeable-Protection-Connector-Electronic/dp/B0D9K7HQHT/ref=sr_1_2?crid=2DU0K654X7ES2&amp;dib=eyJ2IjoiMSJ9.egLvgPNjVgq1LPRu9nAI1kQ3iXFwjIucdG9BRWgdEwKhfmEsgjB6eXKw1uk6TwGr_yVutKJhs_YJ9N24LcnYWIfya0CaKSmAcQdH_6vrJtyGgyNOJraqaUkeeCWETT74zUFxpPa2CBuRYcjWX0_IvG3TJGAqO833tSZuzrln6c3H14OVSYbHMUCLoYHMr6G3WPkwmtfFMa6KVUpIIoz9nh2kTK3nAETxsvpZw4rga8LHOn1HLw0elx0cXSUpujZeAaHEkP7hHSjcJqbwBppaeJnR4-kiVPmdq-t-isLAa5E.NY-KgN1DIEokvCzH_yxnjW5oUW6BRwfvdFum2TA5A58&amp;dib_tag=se&amp;keywords=3.7V%2B1000mAh%2B1S%2B3C%2BLiPo%2BBatteries%2B(4-Pack)%2BRechargeable%2Bwith%2BProtection%2BBoard&amp;nsdOptOutParam=true&amp;qid=1780882135&amp;sprefix=ge%2B1000mah%2Caps%2C374&amp;sr=8-2&amp;th=1</t>
+  </si>
+  <si>
+    <t>MakerHawk 4 Pack 3.7V 1000mAh LiPo Battery Rechargeable</t>
   </si>
   <si>
     <t>Screw M2*4</t>
@@ -83,7 +73,7 @@
     <t>https://www.amazon.com/iexcell-Thread-Socket-Screws-Finish/dp/B0D4JM92FW/ref=sr_1_1?crid=PYQ4ITFNSCRF&amp;dib=eyJ2IjoiMSJ9.I9uoP5aIwVJkDdVEatNGbSC62i-iSe8GGvnKHdCnytaSFrPEVOl4rR8DOf6CTvcqym02NLZrUu1gM1A4E2ZaAkTTXxQwsBhBMIkI59eGOFQZREHaWTxddty74diLDfZOIPYTxLWOKn3plSL9o-n7fwdrxJWS27NKm_G4TQE3GtzfgGkIqvBEoj0jRJXw8iVvV3xtrjR8rqjc2vGyknMkmE0BT9FaIsqlukvPBodJJl8.z_2TwJG4W4xOnxlbcDfOLFBCNTpVjLMO82Ew1hoMl1g&amp;dib_tag=se&amp;keywords=M2*4&amp;qid=1764671189&amp;sprefix=m2%2B4%2Caps%2C955&amp;sr=8-1&amp;th=1</t>
   </si>
   <si>
-    <t>M2*4</t>
+    <t>iexcell 100 Pcs M2 x 4mm</t>
   </si>
   <si>
     <t>Screw M2*6</t>
@@ -92,7 +82,7 @@
     <t>https://www.amazon.com/iexcell-Thread-Socket-Screws-Finish/dp/B0D4JMMJ9M/ref=sr_1_1?crid=PYQ4ITFNSCRF&amp;dib=eyJ2IjoiMSJ9.I9uoP5aIwVJkDdVEatNGbSC62i-iSe8GGvnKHdCnytaSFrPEVOl4rR8DOf6CTvcqym02NLZrUu1gM1A4E2ZaAkTTXxQwsBhBMIkI59eGOFQZREHaWTxddty74diLDfZOIPYTxLWOKn3plSL9o-n7fwdrxJWS27NKm_G4TQE3GtzfgGkIqvBEoj0jRJXw8iVvV3xtrjR8rqjc2vGyknMkmE0BT9FaIsqlukvPBodJJl8.z_2TwJG4W4xOnxlbcDfOLFBCNTpVjLMO82Ew1hoMl1g&amp;dib_tag=se&amp;keywords=M2*4&amp;qid=1764671189&amp;sprefix=m2%2B4%2Caps%2C955&amp;sr=8-1&amp;th=1</t>
   </si>
   <si>
-    <t>M2*6</t>
+    <t>iexcell 100 Pcs M2 x 6mm</t>
   </si>
   <si>
     <t>Screw M2.5*5</t>
@@ -101,7 +91,7 @@
     <t>https://www.amazon.com/iexcell-Thread-Socket-Screws-Finish/dp/B0DDXRMGCW/ref=sr_1_1?crid=PYQ4ITFNSCRF&amp;dib=eyJ2IjoiMSJ9.I9uoP5aIwVJkDdVEatNGbSC62i-iSe8GGvnKHdCnytaSFrPEVOl4rR8DOf6CTvcqym02NLZrUu1gM1A4E2ZaAkTTXxQwsBhBMIkI59eGOFQZREHaWTxddty74diLDfZOIPYTxLWOKn3plSL9o-n7fwdrxJWS27NKm_G4TQE3GtzfgGkIqvBEoj0jRJXw8iVvV3xtrjR8rqjc2vGyknMkmE0BT9FaIsqlukvPBodJJl8.z_2TwJG4W4xOnxlbcDfOLFBCNTpVjLMO82Ew1hoMl1g&amp;dib_tag=se&amp;keywords=M2*4&amp;qid=1764671189&amp;sprefix=m2%2B4%2Caps%2C955&amp;sr=8-1&amp;th=1</t>
   </si>
   <si>
-    <t>M2.5*5</t>
+    <t>iexcell 100 Pcs M2.5 x 5mm</t>
   </si>
   <si>
     <t>Screw M3*6</t>
@@ -110,31 +100,28 @@
     <t>https://www.amazon.com/iexcell-Thread-Socket-Screws-Finish/dp/B07GGXKW1Y/ref=sr_1_1?crid=PYQ4ITFNSCRF&amp;dib=eyJ2IjoiMSJ9.I9uoP5aIwVJkDdVEatNGbSC62i-iSe8GGvnKHdCnytaSFrPEVOl4rR8DOf6CTvcqym02NLZrUu1gM1A4E2ZaAkTTXxQwsBhBMIkI59eGOFQZREHaWTxddty74diLDfZOIPYTxLWOKn3plSL9o-n7fwdrxJWS27NKm_G4TQE3GtzfgGkIqvBEoj0jRJXw8iVvV3xtrjR8rqjc2vGyknMkmE0BT9FaIsqlukvPBodJJl8.z_2TwJG4W4xOnxlbcDfOLFBCNTpVjLMO82Ew1hoMl1g&amp;dib_tag=se&amp;keywords=M2*4&amp;qid=1764671189&amp;sprefix=m2%2B4%2Caps%2C955&amp;sr=8-1&amp;th=1</t>
   </si>
   <si>
-    <t>M3*6</t>
+    <t>iexcell 250 Pcs M3 x 6</t>
   </si>
   <si>
     <t>BigHead Screw M2*6</t>
   </si>
   <si>
-    <t>https://detail.tmall.com/item.htm?id=722946822369&amp;spm=a1z09.2.0.0.6f8c2e8daIyqdB&amp;_u=k2st8hc21ee3</t>
-  </si>
-  <si>
     <t>Nut M2</t>
   </si>
   <si>
     <t>https://www.amazon.com/pouilzx-Carbon-Steel-Hexagon-200pcs/dp/B0CMG7Q27P/ref=sr_1_2?crid=3OM8LUUCAGUOD&amp;dib=eyJ2IjoiMSJ9.hUWxoVt0YqTwEwg0_SRHYmwKSe2NMvFOmtZuhPcAnZxPG3QA0KIGexxB5Ypb_mht9tV0cVZNxN1hCQf296qGkEVK7faUpst5QCryA2oT_3-kG1sPfVZEV3Ud9TYfnYm2wiG9M79ckVHpbJzAz2hwh3IOy9qfSdPrkQNurDP9TTv6BPHdQx3EGadtmxjYt4QuQwsNH2GRmHgrE-Isi6WTGqBb1nWCBjchYaY32maKBwA.gv92mMZhgfqJHgAwGqx1YkKEhm9wUKJkh7lJvt3UpyA&amp;dib_tag=se&amp;keywords=M2+nut&amp;qid=1764671794&amp;sprefix=m2+nut%2Caps%2C940&amp;sr=8-2</t>
   </si>
   <si>
-    <t>M2</t>
+    <t>M2 Carbon Steel Grade 8 Hexagon Hex Nut Black Carbon Steel</t>
   </si>
   <si>
     <t>Screw M2.3*15</t>
   </si>
   <si>
-    <t>https://item.taobao.com/item.htm?spm=a1z09.2.0.0.6f8c2e8daIyqdB&amp;id=538025764032&amp;_u=k2st8hc217d7</t>
-  </si>
-  <si>
-    <t>M2.3*15</t>
+    <t>https://www.amazon.com/uxcell-Stainless-Phillips-Tapping-Screws/dp/B01M0DCMHQ/ref=sr_1_2?crid=2KBKEK42RVBTN&amp;dib=eyJ2IjoiMSJ9.zdyj7-zT7U5wgYw8OP_NBpQm7DpTj2zaMC53BUSnzP_MSOE6xYXlIUtXll0hJxRyh1eYrcsugrZcJw72t5eUICd6dsqob4sJyqEV2pf2VWxfctOoozIpZ_XMb--B1xDTayQWPpPwmX_fPeccfurIxhvRZe8P0FvLoQcxa6TZ7gqI8dcBxXCnJ7zklgwzA57prelDN0CKeJj4M_6R3ZvR9a-0iCTaU-3DGPwd0Wc6cqM.d0TgoGGhMa7SmLQD2JuIsMYr4c1NWlAqe9Y0-ipUwJ0&amp;dib_tag=se&amp;keywords=iexcell+100+Pcs+M2.3+x+15mm&amp;qid=1780882452&amp;sprefix=iexcell+100+pcs+m2.3+x+1mm%2Caps%2C350&amp;sr=8-2</t>
+  </si>
+  <si>
+    <t>uxcell 100 Pcs M2.5 x 15mm Stainless Steel Phillips Round Head Self Tapping Screws Bolts</t>
   </si>
   <si>
     <t>Earings 3-6-2</t>
@@ -143,7 +130,7 @@
     <t>https://www.amazon.com/Hobbypark-Bearings-Shielded-Quadcopter-Helicopter/dp/B019F2ZH92/ref=sr_1_1?crid=1IJ1TB1A64E27&amp;dib=eyJ2IjoiMSJ9.TfDoCBZZHys2lKMa4-OUDKkdnRHj_ydZqtt6YuX9y-AOwMfBfaytk_mqVzWqAdLbE5L-RPfdERZBMpfwm5BYCwIvjYqbXvwuj9FE49Hf8t1nSlE3AKxVQtmToTOC7zHIsX-D9eTZeHDWDvtdOWRV2in7L6xnVZKrEHF4R1GPFlNiRNtBXmHzPvGkc8c25n-x6tj4cny6dn4XmVkeq9CJOoMh8zRBV5kbNa2vA_lwSKw.fjCRsVkge6ZH_7fhrEIPpCp7bKsCf3VYIPdmb6Y3vpU&amp;dib_tag=se&amp;keywords=bearing+3*6*2&amp;qid=1764672471&amp;sprefix=bearing+3+6+2%2Caps%2C411&amp;sr=8-1</t>
   </si>
   <si>
-    <t>3*6*2</t>
+    <t>10pcs Hobbypark Micro Ball Bearings 3x6x2mm</t>
   </si>
   <si>
     <t>Earings 4-7-2.5</t>
@@ -152,7 +139,7 @@
     <t>https://www.amazon.com/4x7x2-5-Shielded-Precision-Miniature-Bearings/dp/B085RD75QY/ref=sr_1_1?crid=3AKHKFTN1K50W&amp;dib=eyJ2IjoiMSJ9.pHq_oFkqlm8pw1g2jO1OFnKskziiucwYGsrCE3QaWjjy4SnWh8YeZq7-4umDzgwIrZ_CA4Mvc0iA3PkV9YeF783n_PPFnK1oa8Wc3OdmIZBCI0oZ15i2WuftGkx7kn2-TDHEef5c1E0tSYytS7Nr7ZOQJbjLmh81XlyUxHhmQba8yWpc85D8P5ntCPZkMnE8ZJw7uqVe3TeSezuuIzgyBEzR6b3mq7aur5iR1ZP7T4I.fWdlR9x5165RhSK3CBXZYZs62zHP353Q4hvaZN7ckZ8&amp;dib_tag=se&amp;keywords=bearing+4*7*2.5&amp;qid=1764672568&amp;sprefix=bearing+4+7+2.5%2Caps%2C623&amp;sr=8-1</t>
   </si>
   <si>
-    <t>4*7*2.5</t>
+    <t>10 Pack 4x7x2.5 Metal Shielded ABEC-5 High Precision Miniature Ball Bearings L-740ZZ (MR74ZZ)</t>
   </si>
   <si>
     <t>Cylindrical Pin 4x12</t>
@@ -161,7 +148,7 @@
     <t>https://www.amazon.com/uxcell-Stainless-Cylindrical-Support-Elements/dp/B07YKYJZ63/ref=sr_1_2?crid=4IFZ6VCZJT6W&amp;dib=eyJ2IjoiMSJ9.GQtZL0ulAQWcyXBb1IRQxAlKK-JPyJ4I0LsRVSlpJV_2zU2U31SaNkk5vK85Not-bc6j0rlCwQeHoxdU1FzuKT5xTVHyCpzTUmIJ4-B4NdIkqwPJgAscT6v27h0rkvEfw482HV_3hx16YvFHFlZYaogqUi8WJkDloiVqLfAludSSPJ6uAMcV8QwQKPbBlwoo.jkNhTWlt21izna43v_qq3jLCC7o338O_p7i7c79LHNE&amp;dib_tag=se&amp;keywords=cylindrical%2Bpin%2B4*12&amp;qid=1764672652&amp;sprefix=cylindrical%2Bpin%2B4%2B12%2Caps%2C356&amp;sr=8-2&amp;th=1</t>
   </si>
   <si>
-    <t>4*12</t>
+    <t>uxcell 4 x 12mm(Approx 5/32") Dowel Pin 304 Stainless Steel Wood Bunk Bed Dowel Pins Shelf Pegs Support Shelves 25Pcs</t>
   </si>
   <si>
     <t>Brass Standoff M2*8+3</t>
@@ -170,7 +157,7 @@
     <t>https://www.amazon.com/MECCANIXITY-Standoffs-Assortment-Raspberry-Motherboard/dp/B0FH1FTF5J/ref=sr_1_6?crid=2D7ZN6PJ0AKGU&amp;dib=eyJ2IjoiMSJ9.8IxbMudrwQ1gS1WBHJ_NvfApQGxa4RC6O22nHbBY9JC7YMSjjRYN9Kcs95xlV3MfLN4EDPi6nXo_fSLEK5QaQgUmS3DMaKa7yFPgTOXM81yi72JXMuef28KJXF8BUUk30YylhbR04KdUYBap8ibwm6tZwSiieqskxs-RmpushHJ_DfWlIubyyYRvEkymz6V_uYaTdLKhWt7C5oAVQqZNjvhESkiYdjwsEmOk7wLT7LI.uQnH7iRTj9hvEgYAYzoJN4eTCGcmNMXul-gadhV4XpE&amp;dib_tag=se&amp;keywords=brass%2Bstandoffs%2Bm2*8&amp;qid=1764672834&amp;sprefix=brass%2Bstandoffs%2Bm2%2B8%2Caps%2C426&amp;sr=8-6&amp;th=1</t>
   </si>
   <si>
-    <t>M2*8+3</t>
+    <t>MECCANIXITY M2 Male Brass Hex Spacer Standoffs Screws Nuts, 20 Set Hex Column Screw Nut Assortment Kit M2*8+3 Threaded Standoff</t>
   </si>
   <si>
     <t>Brass Standoff M2*25+4</t>
@@ -179,7 +166,7 @@
     <t>https://www.amazon.com/PATIKIL-Standoff-Quadcopter-Motherboard-Computer/dp/B0DWF384DG/ref=sr_1_14?crid=28FHC3D7R9Z4D&amp;dib=eyJ2IjoiMSJ9.N_qh4mqXoluqI9AfdurMjo-FmfE1lOrVz_b3vl82T3aciultdUcz9_jr63J0OGOr9-4w5hL7oXQHbe_K93hXWAasDQWFHpUFDRaSxuTx63uCnsz4Nt649Sp8Ca_zfjhzL2C2vJtUQFI4sN3vILSKCeuXfiwDeTiwmviWxFEVFrfrICgGIxi8K7C11x_KLr8lscjQ4KIj9iu3iZMlY4k9qHVTG3rIJnTy8CRUfMOBVck.Z63ehHu2RN7wKH3u3BJYE33L8cnN2HH1no05XEDovtI&amp;dib_tag=se&amp;keywords=brass%2Bstandoffs%2Bm2*25&amp;qid=1764673038&amp;sprefix=brass%2Bstandoffs%2Bm2%2B25%2B%2Caps%2C1314&amp;sr=8-14&amp;th=1</t>
   </si>
   <si>
-    <t>M2*25+4</t>
+    <t>PATIKIL M2 x 20+3 mm Male Female Brass Hex Spacer Standoff</t>
   </si>
   <si>
     <t>Brass Standoff M2*8</t>
@@ -188,7 +175,7 @@
     <t>https://www.amazon.com/uxcell-Straight-Pillar-Standoff-M2x3x8mm/dp/B07H3SR8XX/ref=sr_1_1?crid=22GD2WBJM4T6R&amp;dib=eyJ2IjoiMSJ9.RgTnu8eTeo9HgMfjKSirbbzlrK7VUOMMW_Tetj9_uBW7YMSjjRYN9Kcs95xlV3Mf4G409qMg1_-41nx0ygYRGijhGsoqMlcaM8EwnuSb7uJjPp3oHmrzf0UEW4eIJ7xkFxObsAsFyK-DYkXwqtbtB8t_qVKVsS1lIMfR8WBf6DdpfPJ752u7cX2HQWjU6srcWXXm6cKo7RbB9d077hovpGkgmHpHh2KAjv0qd4rUeSI.1h2V5Zz6MWxfO_UFoV4SthSJYRHqemayKoiJ7oP25do&amp;dib_tag=se&amp;keywords=M2*8+brass+standoff&amp;qid=1764673852&amp;sprefix=m2+8+brass+standoff%2Caps%2C459&amp;sr=8-1</t>
   </si>
   <si>
-    <t>M2*8</t>
+    <t>uxcell 50pcs Brass Round Straight PCB Pillar Female Thread Standoff Spacer M2x3x8mm</t>
   </si>
   <si>
     <t>Brass Standoff M2*3*3</t>
@@ -197,7 +184,7 @@
     <t>https://www.amazon.com/uxcell-116pcs-Straight-Standoff-M2x3x3mm/dp/B07H3XJ7BB/ref=sr_1_2_sspa?crid=I18JF6N5XGV4&amp;dib=eyJ2IjoiMSJ9.gQrsJdjPio93kgEjHgW-4XW7Mb8U2JLjAC69J_OOVO_dAcQa__pK6mUT9LOFSV5YTOQWysEg_ydVKe_2R3pjHbgJDwWiqDDf-T2zb44YuyhQJpkrQPbclfVSmxHhjXr80am7RVGnmaPxitY5jHEPIVuh5PwPlOGg_57jkLg1zl51OAy9Z0N2datWjJdp4hZWKI6urnqAj5heKr7g1txqSK7wwKfh7-en2K4Rf2yoV3Y.Fs_COGMDQD-jL32D2JuKVAYtb3kO-2Y8HySBpIDGVpc&amp;dib_tag=se&amp;keywords=brass+standoff+M2+3*3&amp;qid=1764673961&amp;sprefix=brass+standoff+m2+3+3%2Caps%2C433&amp;sr=8-2-spons&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9hdGY&amp;psc=1</t>
   </si>
   <si>
-    <t>M2 w3*h3</t>
+    <t>uxcell 116pcs Brass Round Straight PCB Pillar Female Thread Standoff Spacer M2x3x3mm</t>
   </si>
   <si>
     <t>Tire（Round Silicone Ring）</t>
@@ -206,16 +193,16 @@
     <t>https://www.amazon.com/Rubber-Assorted-Camping-Survival-Supplies/dp/B0BX4CYWB7/ref=sr_1_14?crid=B4AZ1YKM5D5N&amp;dib=eyJ2IjoiMSJ9.UFjdkXme7AA5dRx-2oC-AVCcSF6h5f7alhoxn5XH8GP1qJjO_ip9Aw1dg9oM8rN-9JIm5TMtKGnm5Tnr8Y9twSX5oy49r7DB724I9AfeqC1XQmwsxYtzAMG1ty05tDkJrTAA4QdAqHVN4f3QQs-Utg7FybPIGakgGtZeg1gWMC_mxeNiVAZIlLzwSaHSq5FXD44lks4X2RsTf1erGKGxl5USRk8Y4VoYn1fvQEtMyeOSKIkH-H-XHdR2Y0EFVIYD-Sd3y1j1ZYaRr5htTUyiBH5k9FM1WcEvu5Rtqq1KjdE.yeuMQysCZyUwRG4bb6f6EVyZOUDtI2ovu7416UOF3EE&amp;dib_tag=se&amp;keywords=wide%2Brubber%2Bband&amp;qid=1764674185&amp;sprefix=wide%2Brubber%2Bband%2Caps%2C512&amp;sr=8-14&amp;th=1</t>
   </si>
   <si>
-    <t>Diameter 25 Width 10mm Black</t>
+    <t>60 Mixed Count Heavy Duty Rubber Bands 6 Size Black Thick</t>
   </si>
   <si>
     <t>OLED</t>
   </si>
   <si>
-    <t>https://item.taobao.com/item.htm?id=769782683401&amp;mi_id=0000UFHJoeb-xtXOu18RgX2iVQ_QV8OTsgxMMTlWHDn3UxM&amp;spm=tbpc.boughtlist.suborder_itemtitle.1.1b2a2e8damrYGA</t>
-  </si>
-  <si>
-    <t>1.21 inches</t>
+    <t>https://www.amazon.com/Hosyond-Display-3-3V-5V-Compatible-Raspberry/dp/B0BWJLV39P/ref=sr_1_15?crid=3ICBP8QFE30XR&amp;dib=eyJ2IjoiMSJ9.6uJuI5cggaMKzcvI3mu-du9ZCMzlO-dvgULIyGL_l8IvxPaOEP_GCf7hlIBMcRREiXg2fWz7Cs4SZCjSR_7WSmbTicjXrz2Bpo4yD96TF-2gSqXkMsphjAajtDdLVmfvg3xvN8e2l9rxkT6GE1jUQuEoQtw-ggprEVSTJ51n0sG8pnrxkwpfDKYHNM-JqI-BaUo8fD22sJU9JJbK9qzyyMLlFJ-yWsT04oVg7Mj6Ry4.vHL6PlW1M5U7_20FfgSkh4QHu_VE0WNOoFhmBZ3ubcg&amp;dib_tag=se&amp;keywords=OLED%2B1.21%2Binches&amp;qid=1780882988&amp;sprefix=oled%2B1.21%2Binches%2Caps%2C467&amp;sr=8-15&amp;th=1</t>
+  </si>
+  <si>
+    <t>0.91 Inch I2C IIC OLED Display Module OLED</t>
   </si>
   <si>
     <t>sh1.0 4P</t>
@@ -224,7 +211,7 @@
     <t>https://www.amazon.com/Pre-Crimped-Connectors-SPRacingF3-Omnibus-Silicone/dp/B07PDQKHJ2/ref=sr_1_2?crid=121FJ5WRAUDJV&amp;dib=eyJ2IjoiMSJ9.Mnmg9cJrrWFJvQ5a9TnUEjeZq6mS-Ppv5D0VMbDcFgC5PWeQUxEoH7dDX_tcKBx6jxLpt2yJEGCdxxtbjjpDZIwSEeofSTFeC66scCsLB8T4NzElfFzcderHntyx6Sb758XlI0Wrbb5snUzVpNV75RuGnzJqck8mGYdP-5ZvZCp0O9TDs2BvAX4cauMaQtFI7NxAQp-pIuOALg5_KcUaEjL82f17JBGMyj5jPRmOzzDAoLFouiJuDZVIRmq1_K79zrNPgbLwZOSONPG_39uVcbqvwkjaH9ez8jRdOJYkKcQ.AuraxtE6zJgiz2mePhsDVmTAU0tI1S59LBRjLdJkzNE&amp;dib_tag=se&amp;keywords=sh1.0+4P&amp;qid=1764673453&amp;sprefix=sh1.0+4p%2Caps%2C385&amp;sr=8-2</t>
   </si>
   <si>
-    <t>150mm</t>
+    <t>SH1.0 Connectors and Pre-Crimped Silicone Cables Compatible with JST SH 1.0mm</t>
   </si>
   <si>
     <t>MX1.27 7P</t>
@@ -233,16 +220,16 @@
     <t>https://www.amazon.com/HFHYDZSW-MX1-25-1-25mm-Connector-Head_10PCS_7P/dp/B0DSTVJBH2/ref=sr_1_4?crid=3U38PMH42H40L&amp;dib=eyJ2IjoiMSJ9.iQPI25cX4s0cJQ-KKO3sbxDCPfzyTlmPY6yGcBhnFxXyY2ImqB6ebMRGZGWBMFnkx92qitPXGUBs2A9-icKYKCSodUz4Q7BYMGF7lF3gUhBVnSqBTbt0H4tTHoG4sof4HzhqF9dzda6khevIbzhgOlYhHZIIjDSGREtUcBwyQWAUIpRm02gc48Ij5S3UaiQw.a7yQE7_4qJOBz5dgtPrYDdicixtD-A1VVlTbosZk_GI&amp;dib_tag=se&amp;keywords=MX1.25%2B7p&amp;qid=1764673631&amp;sprefix=mx1.25%2B7p%2Caps%2C372&amp;sr=8-4&amp;th=1</t>
   </si>
   <si>
-    <t>10mm</t>
+    <t>HFHYDZSW 10PCS JST 10mm Wire Cable</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
@@ -284,10 +271,86 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -308,45 +371,13 @@
     </font>
     <font>
       <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FFFFFFFF"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="宋体"/>
@@ -354,24 +385,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF9C6500"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -383,34 +398,6 @@
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="33">
     <fill>
@@ -433,175 +420,175 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -612,6 +599,15 @@
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -626,24 +622,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -678,6 +656,26 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="double">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -701,164 +699,153 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="22" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -872,13 +859,13 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="6">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="10">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="6" applyFont="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="10" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -887,52 +874,52 @@
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="货币[0]" xfId="1" builtinId="7"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="2" builtinId="38"/>
+    <cellStyle name="输入" xfId="3" builtinId="20"/>
+    <cellStyle name="货币" xfId="4" builtinId="4"/>
+    <cellStyle name="千位分隔[0]" xfId="5" builtinId="6"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="6" builtinId="39"/>
+    <cellStyle name="差" xfId="7" builtinId="27"/>
+    <cellStyle name="千位分隔" xfId="8" builtinId="3"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="9" builtinId="40"/>
+    <cellStyle name="超链接" xfId="10" builtinId="8"/>
+    <cellStyle name="百分比" xfId="11" builtinId="5"/>
+    <cellStyle name="已访问的超链接" xfId="12" builtinId="9"/>
+    <cellStyle name="注释" xfId="13" builtinId="10"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="14" builtinId="36"/>
     <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="警告文本" xfId="16" builtinId="11"/>
+    <cellStyle name="标题" xfId="17" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="18" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="19" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="20" builtinId="17"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="21" builtinId="32"/>
+    <cellStyle name="标题 3" xfId="22" builtinId="18"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="23" builtinId="44"/>
+    <cellStyle name="输出" xfId="24" builtinId="21"/>
+    <cellStyle name="计算" xfId="25" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="26" builtinId="23"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="27" builtinId="50"/>
+    <cellStyle name="强调文字颜色 2" xfId="28" builtinId="33"/>
+    <cellStyle name="链接单元格" xfId="29" builtinId="24"/>
+    <cellStyle name="汇总" xfId="30" builtinId="25"/>
+    <cellStyle name="好" xfId="31" builtinId="26"/>
+    <cellStyle name="适中" xfId="32" builtinId="28"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="33" builtinId="46"/>
+    <cellStyle name="强调文字颜色 1" xfId="34" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="35" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="36" builtinId="31"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="37" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="38" builtinId="35"/>
+    <cellStyle name="强调文字颜色 3" xfId="39" builtinId="37"/>
+    <cellStyle name="强调文字颜色 4" xfId="40" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="41" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="42" builtinId="43"/>
+    <cellStyle name="强调文字颜色 5" xfId="43" builtinId="45"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="44" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="45" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="46" builtinId="49"/>
     <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
@@ -1129,7 +1116,7 @@
     </dxf>
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
-    <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
+    <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7">
       <tableStyleElement type="wholeTable" dxfId="6"/>
       <tableStyleElement type="headerRow" dxfId="5"/>
       <tableStyleElement type="totalRow" dxfId="4"/>
@@ -1138,7 +1125,7 @@
       <tableStyleElement type="firstRowStripe" dxfId="1"/>
       <tableStyleElement type="firstColumnStripe" dxfId="0"/>
     </tableStyle>
-    <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
+    <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10">
       <tableStyleElement type="headerRow" dxfId="16"/>
       <tableStyleElement type="totalRow" dxfId="15"/>
       <tableStyleElement type="firstRowStripe" dxfId="14"/>
@@ -1409,16 +1396,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D23"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="3"/>
+  <dimension ref="A1:E23"/>
+  <sheetFormatPr defaultColWidth="8.89090909090909" defaultRowHeight="14" outlineLevelCol="4"/>
   <cols>
-    <col min="1" max="1" width="30.3333333333333" customWidth="1"/>
-    <col min="2" max="2" width="29.5555555555556" customWidth="1"/>
-    <col min="3" max="3" width="19" customWidth="1"/>
-    <col min="4" max="4" width="14.4444444444444" customWidth="1"/>
+    <col min="1" max="1" width="30.3363636363636" customWidth="1"/>
+    <col min="2" max="2" width="29.5545454545455" customWidth="1"/>
+    <col min="3" max="3" width="26.5454545454545" customWidth="1"/>
+    <col min="4" max="4" width="14.4454545454545" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1431,138 +1418,168 @@
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" spans="1:4">
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
       <c r="A2" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" t="s">
         <v>5</v>
       </c>
+      <c r="B2" s="3" t="s">
+        <v>6</v>
+      </c>
       <c r="C2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D2">
         <v>2</v>
       </c>
-    </row>
-    <row r="3" spans="1:4">
+      <c r="E2">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
       <c r="A3" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D3">
         <v>2</v>
       </c>
-    </row>
-    <row r="4" spans="1:4">
+      <c r="E3">
+        <v>16.31</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
       <c r="A4" s="4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D4">
         <v>2</v>
       </c>
-    </row>
-    <row r="5" spans="1:4">
+      <c r="E4">
+        <v>8.99</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
       <c r="A5" s="6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D5">
         <v>1</v>
       </c>
-    </row>
-    <row r="6" spans="1:4">
+      <c r="E5">
+        <v>18.99</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
       <c r="A6" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D6">
         <v>20</v>
       </c>
-    </row>
-    <row r="7" spans="1:4">
+      <c r="E6">
+        <v>7.86</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
       <c r="A7" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C7" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D7">
         <v>10</v>
       </c>
-    </row>
-    <row r="8" spans="1:4">
+      <c r="E7">
+        <v>7.86</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
       <c r="A8" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C8" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D8">
         <v>10</v>
       </c>
-    </row>
-    <row r="9" spans="1:4">
+      <c r="E8">
+        <v>7.86</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
       <c r="A9" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C9" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D9">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:4">
+      <c r="E9">
+        <v>9.86</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
       <c r="A10" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="B10" t="s">
         <v>29</v>
       </c>
+      <c r="B10" s="3" t="s">
+        <v>21</v>
+      </c>
       <c r="C10" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D10">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:4">
+      <c r="E10">
+        <v>7.86</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
       <c r="A11" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B11" s="3" t="s">
         <v>31</v>
       </c>
       <c r="C11" t="s">
@@ -1571,12 +1588,15 @@
       <c r="D11">
         <v>10</v>
       </c>
-    </row>
-    <row r="12" spans="1:4">
+      <c r="E11">
+        <v>5.99</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
       <c r="A12" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B12" s="3" t="s">
         <v>34</v>
       </c>
       <c r="C12" t="s">
@@ -1585,12 +1605,15 @@
       <c r="D12">
         <v>2</v>
       </c>
-    </row>
-    <row r="13" spans="1:4">
+      <c r="E12">
+        <v>9.29</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
       <c r="A13" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B13" s="3" t="s">
         <v>37</v>
       </c>
       <c r="C13" t="s">
@@ -1599,12 +1622,15 @@
       <c r="D13">
         <v>4</v>
       </c>
-    </row>
-    <row r="14" spans="1:4">
+      <c r="E13">
+        <v>8.97</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
       <c r="A14" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B14" s="3" t="s">
         <v>40</v>
       </c>
       <c r="C14" t="s">
@@ -1613,12 +1639,15 @@
       <c r="D14">
         <v>4</v>
       </c>
-    </row>
-    <row r="15" spans="1:4">
+      <c r="E14">
+        <v>9.49</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
       <c r="A15" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B15" s="3" t="s">
         <v>43</v>
       </c>
       <c r="C15" t="s">
@@ -1627,12 +1656,15 @@
       <c r="D15">
         <v>2</v>
       </c>
-    </row>
-    <row r="16" spans="1:4">
+      <c r="E15">
+        <v>7.69</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5">
       <c r="A16" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="B16" t="s">
+      <c r="B16" s="3" t="s">
         <v>46</v>
       </c>
       <c r="C16" t="s">
@@ -1641,12 +1673,15 @@
       <c r="D16">
         <v>2</v>
       </c>
-    </row>
-    <row r="17" spans="1:4">
+      <c r="E16">
+        <v>7.69</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
       <c r="A17" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="B17" t="s">
+      <c r="B17" s="3" t="s">
         <v>49</v>
       </c>
       <c r="C17" t="s">
@@ -1655,12 +1690,15 @@
       <c r="D17">
         <v>2</v>
       </c>
-    </row>
-    <row r="18" spans="1:4">
+      <c r="E17">
+        <v>5.09</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
       <c r="A18" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="B18" t="s">
+      <c r="B18" s="3" t="s">
         <v>52</v>
       </c>
       <c r="C18" t="s">
@@ -1669,12 +1707,15 @@
       <c r="D18">
         <v>2</v>
       </c>
-    </row>
-    <row r="19" spans="1:4">
+      <c r="E18">
+        <v>7.59</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
       <c r="A19" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="B19" t="s">
+      <c r="B19" s="3" t="s">
         <v>55</v>
       </c>
       <c r="C19" t="s">
@@ -1683,12 +1724,15 @@
       <c r="D19">
         <v>4</v>
       </c>
-    </row>
-    <row r="20" spans="1:4">
+      <c r="E19">
+        <v>8.59</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
       <c r="A20" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="B20" t="s">
+      <c r="B20" s="3" t="s">
         <v>58</v>
       </c>
       <c r="C20" t="s">
@@ -1697,8 +1741,11 @@
       <c r="D20">
         <v>2</v>
       </c>
-    </row>
-    <row r="21" spans="1:4">
+      <c r="E20">
+        <v>9.99</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
       <c r="A21" s="6" t="s">
         <v>60</v>
       </c>
@@ -1711,12 +1758,15 @@
       <c r="D21">
         <v>1</v>
       </c>
-    </row>
-    <row r="22" spans="1:4">
+      <c r="E21">
+        <v>13.99</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
       <c r="A22" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="B22" t="s">
+      <c r="B22" s="3" t="s">
         <v>64</v>
       </c>
       <c r="C22" t="s">
@@ -1725,12 +1775,15 @@
       <c r="D22">
         <v>2</v>
       </c>
-    </row>
-    <row r="23" spans="1:4">
+      <c r="E22">
+        <v>19.99</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
       <c r="A23" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="B23" t="s">
+      <c r="B23" s="3" t="s">
         <v>67</v>
       </c>
       <c r="C23" t="s">
@@ -1739,17 +1792,34 @@
       <c r="D23">
         <v>1</v>
       </c>
+      <c r="E23">
+        <v>19.26</v>
+      </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="B9" r:id="rId1" display="https://www.amazon.com/iexcell-Thread-Socket-Screws-Finish/dp/B07GGXKW1Y/ref=sr_1_1?crid=PYQ4ITFNSCRF&amp;dib=eyJ2IjoiMSJ9.I9uoP5aIwVJkDdVEatNGbSC62i-iSe8GGvnKHdCnytaSFrPEVOl4rR8DOf6CTvcqym02NLZrUu1gM1A4E2ZaAkTTXxQwsBhBMIkI59eGOFQZREHaWTxddty74diLDfZOIPYTxLWOKn3plSL9o-n7fwdrxJWS27NKm_G4TQE3GtzfgGkIqvBEoj0jRJXw8iVvV3xtrjR8rqjc2vGyknMkmE0BT9FaIsqlukvPBodJJl8.z_2TwJG4W4xOnxlbcDfOLFBCNTpVjLMO82Ew1hoMl1g&amp;dib_tag=se&amp;keywords=M2*4&amp;qid=1764671189&amp;sprefix=m2%2B4%2Caps%2C955&amp;sr=8-1&amp;th=1"/>
-    <hyperlink ref="B8" r:id="rId2" display="https://www.amazon.com/iexcell-Thread-Socket-Screws-Finish/dp/B0DDXRMGCW/ref=sr_1_1?crid=PYQ4ITFNSCRF&amp;dib=eyJ2IjoiMSJ9.I9uoP5aIwVJkDdVEatNGbSC62i-iSe8GGvnKHdCnytaSFrPEVOl4rR8DOf6CTvcqym02NLZrUu1gM1A4E2ZaAkTTXxQwsBhBMIkI59eGOFQZREHaWTxddty74diLDfZOIPYTxLWOKn3plSL9o-n7fwdrxJWS27NKm_G4TQE3GtzfgGkIqvBEoj0jRJXw8iVvV3xtrjR8rqjc2vGyknMkmE0BT9FaIsqlukvPBodJJl8.z_2TwJG4W4xOnxlbcDfOLFBCNTpVjLMO82Ew1hoMl1g&amp;dib_tag=se&amp;keywords=M2*4&amp;qid=1764671189&amp;sprefix=m2%2B4%2Caps%2C955&amp;sr=8-1&amp;th=1"/>
-    <hyperlink ref="B7" r:id="rId3" display="https://www.amazon.com/iexcell-Thread-Socket-Screws-Finish/dp/B0D4JMMJ9M/ref=sr_1_1?crid=PYQ4ITFNSCRF&amp;dib=eyJ2IjoiMSJ9.I9uoP5aIwVJkDdVEatNGbSC62i-iSe8GGvnKHdCnytaSFrPEVOl4rR8DOf6CTvcqym02NLZrUu1gM1A4E2ZaAkTTXxQwsBhBMIkI59eGOFQZREHaWTxddty74diLDfZOIPYTxLWOKn3plSL9o-n7fwdrxJWS27NKm_G4TQE3GtzfgGkIqvBEoj0jRJXw8iVvV3xtrjR8rqjc2vGyknMkmE0BT9FaIsqlukvPBodJJl8.z_2TwJG4W4xOnxlbcDfOLFBCNTpVjLMO82Ew1hoMl1g&amp;dib_tag=se&amp;keywords=M2*4&amp;qid=1764671189&amp;sprefix=m2%2B4%2Caps%2C955&amp;sr=8-1&amp;th=1"/>
-    <hyperlink ref="B6" r:id="rId4" display="https://www.amazon.com/iexcell-Thread-Socket-Screws-Finish/dp/B0D4JM92FW/ref=sr_1_1?crid=PYQ4ITFNSCRF&amp;dib=eyJ2IjoiMSJ9.I9uoP5aIwVJkDdVEatNGbSC62i-iSe8GGvnKHdCnytaSFrPEVOl4rR8DOf6CTvcqym02NLZrUu1gM1A4E2ZaAkTTXxQwsBhBMIkI59eGOFQZREHaWTxddty74diLDfZOIPYTxLWOKn3plSL9o-n7fwdrxJWS27NKm_G4TQE3GtzfgGkIqvBEoj0jRJXw8iVvV3xtrjR8rqjc2vGyknMkmE0BT9FaIsqlukvPBodJJl8.z_2TwJG4W4xOnxlbcDfOLFBCNTpVjLMO82Ew1hoMl1g&amp;dib_tag=se&amp;keywords=M2*4&amp;qid=1764671189&amp;sprefix=m2%2B4%2Caps%2C955&amp;sr=8-1&amp;th=1"/>
-    <hyperlink ref="B4" r:id="rId5" display="https://www.amazon.com/TRYMAG-Magnets-Neodymium-Whiteboard-Billboard/dp/B09SL2K4BP/ref=sr_1_1?crid=22JKHNBK7PALG&amp;dib=eyJ2IjoiMSJ9.RLPwftsKniozBWj0uh7U142P6RNz4Q4tko0qF8ScuD1UN5UrZjklVoqmEoHKCs1gy-7B-vu8epw-mLdBleLBRQGU204WQ8Mz3Hkj7LiBt81eNZGcRk9iyBYXrOE4EUTTKvJIZFlT2UKdOIuoPVPzuIVK3wZi3F99HscRW39_0PqbO2ftOCFCYt8y_iwUkWJjGeeyTl6dJpaGgIg5pfOES5M26rosCLV3ycoXuQuOVwU.ue-loQpwydrVQT2-in4isvL6W87LcpdknIpnYfFi5Yc&amp;dib_tag=se&amp;keywords=neodymium%2Bmagnet%2B4x1&amp;qid=1764670685&amp;sprefix=neodymium%2Bmagnet%2B4x%2Caps%2C413&amp;sr=8-1&amp;th=1"/>
-    <hyperlink ref="B3" r:id="rId6" display="https://www.amazon.com/Fityle-Gimbal-Brushless-100-200g-Quadcopter/dp/B07JLSL8ZV/ref=sr_1_13?crid=24M2HR8C6IM58&amp;dib=eyJ2IjoiMSJ9.GD2eP8zLbh39g3qy2nAGsGbCBnbohYPT-8UpA_Z7iXVh91pQHkVDFBFsig_IEjEL3Sffd_ST1EdUJAcRiKS1tWHN-Gqw70BZx1US2EIKlJpQmmRUfnBFuL8ZQI_5S6WuusbsSHjlyBuc9rktqq9FOCtrWQt5PCX9QuhE0secsAo-37dyzI7amI25GrDXeQjwyn_Zb-m0PObfGWhbFPP86QegpBuUqFl7npJ002xeMBS5nUfW9Ka1CS4Vc9k92e92QQHodT7KgXjz-XbsqSQxAXFXZl0zMOIaXlC_79vJR5E.VX62aCxSFDlVT0HlIfVQERrn-j-P9X6Dk706DP-i7NI&amp;dib_tag=se&amp;keywords=2208+MOTOR&amp;qid=1764670475&amp;sprefix=2208+motor%2Caps%2C564&amp;sr=8-13"/>
-    <hyperlink ref="B5" r:id="rId7" display="https://item.taobao.com/item.htm?id=559166020526&amp;mi_id=0000fFtHFvsNuZeTME9MVwduHvvvFWSfuFDbCS_zVGx7Vf0&amp;spm=tbpc.boughtlist.suborder_itempic.d559166020526.1b2a2e8damrYGA" tooltip="https://item.taobao.com/item.htm?id=559166020526&amp;mi_id=0000fFtHFvsNuZeTME9MVwduHvvvFWSfuFDbCS_zVGx7Vf0&amp;spm=tbpc.boughtlist.suborder_itempic.d559166020526.1b2a2e8damrYGA"/>
-    <hyperlink ref="B21" r:id="rId8" display="https://item.taobao.com/item.htm?id=769782683401&amp;mi_id=0000UFHJoeb-xtXOu18RgX2iVQ_QV8OTsgxMMTlWHDn3UxM&amp;spm=tbpc.boughtlist.suborder_itemtitle.1.1b2a2e8damrYGA"/>
+    <hyperlink ref="B9" r:id="rId1" display="https://www.amazon.com/iexcell-Thread-Socket-Screws-Finish/dp/B07GGXKW1Y/ref=sr_1_1?crid=PYQ4ITFNSCRF&amp;dib=eyJ2IjoiMSJ9.I9uoP5aIwVJkDdVEatNGbSC62i-iSe8GGvnKHdCnytaSFrPEVOl4rR8DOf6CTvcqym02NLZrUu1gM1A4E2ZaAkTTXxQwsBhBMIkI59eGOFQZREHaWTxddty74diLDfZOIPYTxLWOKn3plSL9o-n7fwdrxJWS27NKm_G4TQE3GtzfgGkIqvBEoj0jRJXw8iVvV3xtrjR8rqjc2vGyknMkmE0BT9FaIsqlukvPBodJJl8.z_2TwJG4W4xOnxlbcDfOLFBCNTpVjLMO82Ew1hoMl1g&amp;dib_tag=se&amp;keywords=M2*4&amp;qid=1764671189&amp;sprefix=m2%2B4%2Caps%2C955&amp;sr=8-1&amp;th=1" tooltip="https://www.amazon.com/iexcell-Thread-Socket-Screws-Finish/dp/B07GGXKW1Y/ref=sr_1_1?crid=PYQ4ITFNSCRF&amp;dib=eyJ2IjoiMSJ9.I9uoP5aIwVJkDdVEatNGbSC62i-iSe8GGvnKHdCnytaSFrPEVOl4rR8DOf6CTvcqym02NLZrUu1gM1A4E2ZaAkTTXxQwsBhBMIkI59eGOFQZREHaWTxddty74diLDfZOIPYTxLWO"/>
+    <hyperlink ref="B8" r:id="rId2" display="https://www.amazon.com/iexcell-Thread-Socket-Screws-Finish/dp/B0DDXRMGCW/ref=sr_1_1?crid=PYQ4ITFNSCRF&amp;dib=eyJ2IjoiMSJ9.I9uoP5aIwVJkDdVEatNGbSC62i-iSe8GGvnKHdCnytaSFrPEVOl4rR8DOf6CTvcqym02NLZrUu1gM1A4E2ZaAkTTXxQwsBhBMIkI59eGOFQZREHaWTxddty74diLDfZOIPYTxLWOKn3plSL9o-n7fwdrxJWS27NKm_G4TQE3GtzfgGkIqvBEoj0jRJXw8iVvV3xtrjR8rqjc2vGyknMkmE0BT9FaIsqlukvPBodJJl8.z_2TwJG4W4xOnxlbcDfOLFBCNTpVjLMO82Ew1hoMl1g&amp;dib_tag=se&amp;keywords=M2*4&amp;qid=1764671189&amp;sprefix=m2%2B4%2Caps%2C955&amp;sr=8-1&amp;th=1" tooltip="https://www.amazon.com/iexcell-Thread-Socket-Screws-Finish/dp/B0DDXRMGCW/ref=sr_1_1?crid=PYQ4ITFNSCRF&amp;dib=eyJ2IjoiMSJ9.I9uoP5aIwVJkDdVEatNGbSC62i-iSe8GGvnKHdCnytaSFrPEVOl4rR8DOf6CTvcqym02NLZrUu1gM1A4E2ZaAkTTXxQwsBhBMIkI59eGOFQZREHaWTxddty74diLDfZOIPYTxLWO"/>
+    <hyperlink ref="B7" r:id="rId3" display="https://www.amazon.com/iexcell-Thread-Socket-Screws-Finish/dp/B0D4JMMJ9M/ref=sr_1_1?crid=PYQ4ITFNSCRF&amp;dib=eyJ2IjoiMSJ9.I9uoP5aIwVJkDdVEatNGbSC62i-iSe8GGvnKHdCnytaSFrPEVOl4rR8DOf6CTvcqym02NLZrUu1gM1A4E2ZaAkTTXxQwsBhBMIkI59eGOFQZREHaWTxddty74diLDfZOIPYTxLWOKn3plSL9o-n7fwdrxJWS27NKm_G4TQE3GtzfgGkIqvBEoj0jRJXw8iVvV3xtrjR8rqjc2vGyknMkmE0BT9FaIsqlukvPBodJJl8.z_2TwJG4W4xOnxlbcDfOLFBCNTpVjLMO82Ew1hoMl1g&amp;dib_tag=se&amp;keywords=M2*4&amp;qid=1764671189&amp;sprefix=m2%2B4%2Caps%2C955&amp;sr=8-1&amp;th=1" tooltip="https://www.amazon.com/iexcell-Thread-Socket-Screws-Finish/dp/B0D4JMMJ9M/ref=sr_1_1?crid=PYQ4ITFNSCRF&amp;dib=eyJ2IjoiMSJ9.I9uoP5aIwVJkDdVEatNGbSC62i-iSe8GGvnKHdCnytaSFrPEVOl4rR8DOf6CTvcqym02NLZrUu1gM1A4E2ZaAkTTXxQwsBhBMIkI59eGOFQZREHaWTxddty74diLDfZOIPYTxLWO"/>
+    <hyperlink ref="B6" r:id="rId4" display="https://www.amazon.com/iexcell-Thread-Socket-Screws-Finish/dp/B0D4JM92FW/ref=sr_1_1?crid=PYQ4ITFNSCRF&amp;dib=eyJ2IjoiMSJ9.I9uoP5aIwVJkDdVEatNGbSC62i-iSe8GGvnKHdCnytaSFrPEVOl4rR8DOf6CTvcqym02NLZrUu1gM1A4E2ZaAkTTXxQwsBhBMIkI59eGOFQZREHaWTxddty74diLDfZOIPYTxLWOKn3plSL9o-n7fwdrxJWS27NKm_G4TQE3GtzfgGkIqvBEoj0jRJXw8iVvV3xtrjR8rqjc2vGyknMkmE0BT9FaIsqlukvPBodJJl8.z_2TwJG4W4xOnxlbcDfOLFBCNTpVjLMO82Ew1hoMl1g&amp;dib_tag=se&amp;keywords=M2*4&amp;qid=1764671189&amp;sprefix=m2%2B4%2Caps%2C955&amp;sr=8-1&amp;th=1" tooltip="https://www.amazon.com/iexcell-Thread-Socket-Screws-Finish/dp/B0D4JM92FW/ref=sr_1_1?crid=PYQ4ITFNSCRF&amp;dib=eyJ2IjoiMSJ9.I9uoP5aIwVJkDdVEatNGbSC62i-iSe8GGvnKHdCnytaSFrPEVOl4rR8DOf6CTvcqym02NLZrUu1gM1A4E2ZaAkTTXxQwsBhBMIkI59eGOFQZREHaWTxddty74diLDfZOIPYTxLWO"/>
+    <hyperlink ref="B4" r:id="rId5" display="https://www.amazon.com/TRYMAG-Magnets-Neodymium-Whiteboard-Billboard/dp/B09SL2K4BP/ref=sr_1_1?crid=22JKHNBK7PALG&amp;dib=eyJ2IjoiMSJ9.RLPwftsKniozBWj0uh7U142P6RNz4Q4tko0qF8ScuD1UN5UrZjklVoqmEoHKCs1gy-7B-vu8epw-mLdBleLBRQGU204WQ8Mz3Hkj7LiBt81eNZGcRk9iyBYXrOE4EUTTKvJIZFlT2UKdOIuoPVPzuIVK3wZi3F99HscRW39_0PqbO2ftOCFCYt8y_iwUkWJjGeeyTl6dJpaGgIg5pfOES5M26rosCLV3ycoXuQuOVwU.ue-loQpwydrVQT2-in4isvL6W87LcpdknIpnYfFi5Yc&amp;dib_tag=se&amp;keywords=neodymium%2Bmagnet%2B4x1&amp;qid=1764670685&amp;sprefix=neodymium%2Bmagnet%2B4x%2Caps%2C413&amp;sr=8-1&amp;th=1" tooltip="https://www.amazon.com/TRYMAG-Magnets-Neodymium-Whiteboard-Billboard/dp/B09SL2K4BP/ref=sr_1_1?crid=22JKHNBK7PALG&amp;dib=eyJ2IjoiMSJ9.RLPwftsKniozBWj0uh7U142P6RNz4Q4tko0qF8ScuD1UN5UrZjklVoqmEoHKCs1gy-7B-vu8epw-mLdBleLBRQGU204WQ8Mz3Hkj7LiBt81eNZGcRk9iyBYXrOE4E"/>
+    <hyperlink ref="B3" r:id="rId6" display="https://www.amazon.com/Fityle-Gimbal-Brushless-100-200g-Quadcopter/dp/B07JLSL8ZV/ref=sr_1_13?crid=24M2HR8C6IM58&amp;dib=eyJ2IjoiMSJ9.GD2eP8zLbh39g3qy2nAGsGbCBnbohYPT-8UpA_Z7iXVh91pQHkVDFBFsig_IEjEL3Sffd_ST1EdUJAcRiKS1tWHN-Gqw70BZx1US2EIKlJpQmmRUfnBFuL8ZQI_5S6WuusbsSHjlyBuc9rktqq9FOCtrWQt5PCX9QuhE0secsAo-37dyzI7amI25GrDXeQjwyn_Zb-m0PObfGWhbFPP86QegpBuUqFl7npJ002xeMBS5nUfW9Ka1CS4Vc9k92e92QQHodT7KgXjz-XbsqSQxAXFXZl0zMOIaXlC_79vJR5E.VX62aCxSFDlVT0HlIfVQERrn-j-P9X6Dk706DP-i7NI&amp;dib_tag=se&amp;keywords=2208+MOTOR&amp;qid=1764670475&amp;sprefix=2208+motor%2Caps%2C564&amp;sr=8-13" tooltip="https://www.amazon.com/Fityle-Gimbal-Brushless-100-200g-Quadcopter/dp/B07JLSL8ZV/ref=sr_1_13?crid=24M2HR8C6IM58&amp;dib=eyJ2IjoiMSJ9.GD2eP8zLbh39g3qy2nAGsGbCBnbohYPT-8UpA_Z7iXVh91pQHkVDFBFsig_IEjEL3Sffd_ST1EdUJAcRiKS1tWHN-Gqw70BZx1US2EIKlJpQmmRUfnBFuL8ZQI_5S6"/>
+    <hyperlink ref="B5" r:id="rId7" display="https://www.amazon.com/MakerHawk-Rechargeable-Protection-Connector-Electronic/dp/B0D9K7HQHT/ref=sr_1_2?crid=2DU0K654X7ES2&amp;dib=eyJ2IjoiMSJ9.egLvgPNjVgq1LPRu9nAI1kQ3iXFwjIucdG9BRWgdEwKhfmEsgjB6eXKw1uk6TwGr_yVutKJhs_YJ9N24LcnYWIfya0CaKSmAcQdH_6vrJtyGgyNOJraqaUkeeCWETT74zUFxpPa2CBuRYcjWX0_IvG3TJGAqO833tSZuzrln6c3H14OVSYbHMUCLoYHMr6G3WPkwmtfFMa6KVUpIIoz9nh2kTK3nAETxsvpZw4rga8LHOn1HLw0elx0cXSUpujZeAaHEkP7hHSjcJqbwBppaeJnR4-kiVPmdq-t-isLAa5E.NY-KgN1DIEokvCzH_yxnjW5oUW6BRwfvdFum2TA5A58&amp;dib_tag=se&amp;keywords=3.7V%2B1000mAh%2B1S%2B3C%2BLiPo%2BBatteries%2B(4-Pack)%2BRechargeable%2Bwith%2BProtection%2BBoard&amp;nsdOptOutParam=true&amp;qid=1780882135&amp;sprefix=ge%2B1000mah%2Caps%2C374&amp;sr=8-2&amp;th=1" tooltip="https://www.amazon.com/MakerHawk-Rechargeable-Protection-Connector-Electronic/dp/B0D9K7HQHT/ref=sr_1_2?crid=2DU0K654X7ES2&amp;dib=eyJ2IjoiMSJ9.egLvgPNjVgq1LPRu9nAI1kQ3iXFwjIucdG9BRWgdEwKhfmEsgjB6eXKw1uk6TwGr_yVutKJhs_YJ9N24LcnYWIfya0CaKSmAcQdH_6vrJtyGgyNOJraq"/>
+    <hyperlink ref="B21" r:id="rId8" display="https://www.amazon.com/Hosyond-Display-3-3V-5V-Compatible-Raspberry/dp/B0BWJLV39P/ref=sr_1_15?crid=3ICBP8QFE30XR&amp;dib=eyJ2IjoiMSJ9.6uJuI5cggaMKzcvI3mu-du9ZCMzlO-dvgULIyGL_l8IvxPaOEP_GCf7hlIBMcRREiXg2fWz7Cs4SZCjSR_7WSmbTicjXrz2Bpo4yD96TF-2gSqXkMsphjAajtDdLVmfvg3xvN8e2l9rxkT6GE1jUQuEoQtw-ggprEVSTJ51n0sG8pnrxkwpfDKYHNM-JqI-BaUo8fD22sJU9JJbK9qzyyMLlFJ-yWsT04oVg7Mj6Ry4.vHL6PlW1M5U7_20FfgSkh4QHu_VE0WNOoFhmBZ3ubcg&amp;dib_tag=se&amp;keywords=OLED%2B1.21%2Binches&amp;qid=1780882988&amp;sprefix=oled%2B1.21%2Binches%2Caps%2C467&amp;sr=8-15&amp;th=1" tooltip="https://www.amazon.com/Hosyond-Display-3-3V-5V-Compatible-Raspberry/dp/B0BWJLV39P/ref=sr_1_15?crid=3ICBP8QFE30XR&amp;dib=eyJ2IjoiMSJ9.6uJuI5cggaMKzcvI3mu-du9ZCMzlO-dvgULIyGL_l8IvxPaOEP_GCf7hlIBMcRREiXg2fWz7Cs4SZCjSR_7WSmbTicjXrz2Bpo4yD96TF-2gSqXkMsphjAajtDdLV"/>
+    <hyperlink ref="B2" r:id="rId9" display="https://www.amazon.com/magnetic-rotating-minibus-steering-black/dp/B0BP645PF9/ref=sr_1_1?crid=3LS7GUSJS60AA&amp;dib=eyJ2IjoiMSJ9.BE-GIc9FaHnRL9psBoLbxkU7ijHDkcEJvYXOaj1mbmAj27dNP-TEUujrx4p-RL03jtV--AeEGoP12WrvAklEwZKhyBDgqntuxtMmb_GO01iH3JglqKW517CkrE9ZtYij_RSWb_cIH2xjQjYbKJBM7SO5kn-_RA3BKb2Ak5xWc3aLV8Fr-fiV-ZKwNqgSy3C0.xqcww89BSFNI306TRwVLMXFfjPNHTSw82tZBhYTCXo8&amp;dib_tag=se&amp;keywords=ST3032&amp;qid=1764674316&amp;sprefix=st3032%2Caps%2C351&amp;sr=8-1" tooltip="https://www.amazon.com/magnetic-rotating-minibus-steering-black/dp/B0BP645PF9/ref=sr_1_1?crid=3LS7GUSJS60AA&amp;dib=eyJ2IjoiMSJ9.BE-GIc9FaHnRL9psBoLbxkU7ijHDkcEJvYXOaj1mbmAj27dNP-TEUujrx4p-RL03jtV--AeEGoP12WrvAklEwZKhyBDgqntuxtMmb_GO01iH3JglqKW517CkrE9ZtYij_R"/>
+    <hyperlink ref="B10" r:id="rId3" display="https://www.amazon.com/iexcell-Thread-Socket-Screws-Finish/dp/B0D4JMMJ9M/ref=sr_1_1?crid=PYQ4ITFNSCRF&amp;dib=eyJ2IjoiMSJ9.I9uoP5aIwVJkDdVEatNGbSC62i-iSe8GGvnKHdCnytaSFrPEVOl4rR8DOf6CTvcqym02NLZrUu1gM1A4E2ZaAkTTXxQwsBhBMIkI59eGOFQZREHaWTxddty74diLDfZOIPYTxLWOKn3plSL9o-n7fwdrxJWS27NKm_G4TQE3GtzfgGkIqvBEoj0jRJXw8iVvV3xtrjR8rqjc2vGyknMkmE0BT9FaIsqlukvPBodJJl8.z_2TwJG4W4xOnxlbcDfOLFBCNTpVjLMO82Ew1hoMl1g&amp;dib_tag=se&amp;keywords=M2*4&amp;qid=1764671189&amp;sprefix=m2%2B4%2Caps%2C955&amp;sr=8-1&amp;th=1"/>
+    <hyperlink ref="B11" r:id="rId10" display="https://www.amazon.com/pouilzx-Carbon-Steel-Hexagon-200pcs/dp/B0CMG7Q27P/ref=sr_1_2?crid=3OM8LUUCAGUOD&amp;dib=eyJ2IjoiMSJ9.hUWxoVt0YqTwEwg0_SRHYmwKSe2NMvFOmtZuhPcAnZxPG3QA0KIGexxB5Ypb_mht9tV0cVZNxN1hCQf296qGkEVK7faUpst5QCryA2oT_3-kG1sPfVZEV3Ud9TYfnYm2wiG9M79ckVHpbJzAz2hwh3IOy9qfSdPrkQNurDP9TTv6BPHdQx3EGadtmxjYt4QuQwsNH2GRmHgrE-Isi6WTGqBb1nWCBjchYaY32maKBwA.gv92mMZhgfqJHgAwGqx1YkKEhm9wUKJkh7lJvt3UpyA&amp;dib_tag=se&amp;keywords=M2+nut&amp;qid=1764671794&amp;sprefix=m2+nut%2Caps%2C940&amp;sr=8-2"/>
+    <hyperlink ref="B12" r:id="rId11" display="https://www.amazon.com/uxcell-Stainless-Phillips-Tapping-Screws/dp/B01M0DCMHQ/ref=sr_1_2?crid=2KBKEK42RVBTN&amp;dib=eyJ2IjoiMSJ9.zdyj7-zT7U5wgYw8OP_NBpQm7DpTj2zaMC53BUSnzP_MSOE6xYXlIUtXll0hJxRyh1eYrcsugrZcJw72t5eUICd6dsqob4sJyqEV2pf2VWxfctOoozIpZ_XMb--B1xDTayQWPpPwmX_fPeccfurIxhvRZe8P0FvLoQcxa6TZ7gqI8dcBxXCnJ7zklgwzA57prelDN0CKeJj4M_6R3ZvR9a-0iCTaU-3DGPwd0Wc6cqM.d0TgoGGhMa7SmLQD2JuIsMYr4c1NWlAqe9Y0-ipUwJ0&amp;dib_tag=se&amp;keywords=iexcell+100+Pcs+M2.3+x+15mm&amp;qid=1780882452&amp;sprefix=iexcell+100+pcs+m2.3+x+1mm%2Caps%2C350&amp;sr=8-2" tooltip="https://www.amazon.com/uxcell-Stainless-Phillips-Tapping-Screws/dp/B01M0DCMHQ/ref=sr_1_2?crid=2KBKEK42RVBTN&amp;dib=eyJ2IjoiMSJ9.zdyj7-zT7U5wgYw8OP_NBpQm7DpTj2zaMC53BUSnzP_MSOE6xYXlIUtXll0hJxRyh1eYrcsugrZcJw72t5eUICd6dsqob4sJyqEV2pf2VWxfctOoozIpZ_XMb--B1xDTay"/>
+    <hyperlink ref="B13" r:id="rId12" display="https://www.amazon.com/Hobbypark-Bearings-Shielded-Quadcopter-Helicopter/dp/B019F2ZH92/ref=sr_1_1?crid=1IJ1TB1A64E27&amp;dib=eyJ2IjoiMSJ9.TfDoCBZZHys2lKMa4-OUDKkdnRHj_ydZqtt6YuX9y-AOwMfBfaytk_mqVzWqAdLbE5L-RPfdERZBMpfwm5BYCwIvjYqbXvwuj9FE49Hf8t1nSlE3AKxVQtmToTOC7zHIsX-D9eTZeHDWDvtdOWRV2in7L6xnVZKrEHF4R1GPFlNiRNtBXmHzPvGkc8c25n-x6tj4cny6dn4XmVkeq9CJOoMh8zRBV5kbNa2vA_lwSKw.fjCRsVkge6ZH_7fhrEIPpCp7bKsCf3VYIPdmb6Y3vpU&amp;dib_tag=se&amp;keywords=bearing+3*6*2&amp;qid=1764672471&amp;sprefix=bearing+3+6+2%2Caps%2C411&amp;sr=8-1"/>
+    <hyperlink ref="B14" r:id="rId13" display="https://www.amazon.com/4x7x2-5-Shielded-Precision-Miniature-Bearings/dp/B085RD75QY/ref=sr_1_1?crid=3AKHKFTN1K50W&amp;dib=eyJ2IjoiMSJ9.pHq_oFkqlm8pw1g2jO1OFnKskziiucwYGsrCE3QaWjjy4SnWh8YeZq7-4umDzgwIrZ_CA4Mvc0iA3PkV9YeF783n_PPFnK1oa8Wc3OdmIZBCI0oZ15i2WuftGkx7kn2-TDHEef5c1E0tSYytS7Nr7ZOQJbjLmh81XlyUxHhmQba8yWpc85D8P5ntCPZkMnE8ZJw7uqVe3TeSezuuIzgyBEzR6b3mq7aur5iR1ZP7T4I.fWdlR9x5165RhSK3CBXZYZs62zHP353Q4hvaZN7ckZ8&amp;dib_tag=se&amp;keywords=bearing+4*7*2.5&amp;qid=1764672568&amp;sprefix=bearing+4+7+2.5%2Caps%2C623&amp;sr=8-1"/>
+    <hyperlink ref="B15" r:id="rId14" display="https://www.amazon.com/uxcell-Stainless-Cylindrical-Support-Elements/dp/B07YKYJZ63/ref=sr_1_2?crid=4IFZ6VCZJT6W&amp;dib=eyJ2IjoiMSJ9.GQtZL0ulAQWcyXBb1IRQxAlKK-JPyJ4I0LsRVSlpJV_2zU2U31SaNkk5vK85Not-bc6j0rlCwQeHoxdU1FzuKT5xTVHyCpzTUmIJ4-B4NdIkqwPJgAscT6v27h0rkvEfw482HV_3hx16YvFHFlZYaogqUi8WJkDloiVqLfAludSSPJ6uAMcV8QwQKPbBlwoo.jkNhTWlt21izna43v_qq3jLCC7o338O_p7i7c79LHNE&amp;dib_tag=se&amp;keywords=cylindrical%2Bpin%2B4*12&amp;qid=1764672652&amp;sprefix=cylindrical%2Bpin%2B4%2B12%2Caps%2C356&amp;sr=8-2&amp;th=1"/>
+    <hyperlink ref="B16" r:id="rId15" display="https://www.amazon.com/MECCANIXITY-Standoffs-Assortment-Raspberry-Motherboard/dp/B0FH1FTF5J/ref=sr_1_6?crid=2D7ZN6PJ0AKGU&amp;dib=eyJ2IjoiMSJ9.8IxbMudrwQ1gS1WBHJ_NvfApQGxa4RC6O22nHbBY9JC7YMSjjRYN9Kcs95xlV3MfLN4EDPi6nXo_fSLEK5QaQgUmS3DMaKa7yFPgTOXM81yi72JXMuef28KJXF8BUUk30YylhbR04KdUYBap8ibwm6tZwSiieqskxs-RmpushHJ_DfWlIubyyYRvEkymz6V_uYaTdLKhWt7C5oAVQqZNjvhESkiYdjwsEmOk7wLT7LI.uQnH7iRTj9hvEgYAYzoJN4eTCGcmNMXul-gadhV4XpE&amp;dib_tag=se&amp;keywords=brass%2Bstandoffs%2Bm2*8&amp;qid=1764672834&amp;sprefix=brass%2Bstandoffs%2Bm2%2B8%2Caps%2C426&amp;sr=8-6&amp;th=1"/>
+    <hyperlink ref="B17" r:id="rId16" display="https://www.amazon.com/PATIKIL-Standoff-Quadcopter-Motherboard-Computer/dp/B0DWF384DG/ref=sr_1_14?crid=28FHC3D7R9Z4D&amp;dib=eyJ2IjoiMSJ9.N_qh4mqXoluqI9AfdurMjo-FmfE1lOrVz_b3vl82T3aciultdUcz9_jr63J0OGOr9-4w5hL7oXQHbe_K93hXWAasDQWFHpUFDRaSxuTx63uCnsz4Nt649Sp8Ca_zfjhzL2C2vJtUQFI4sN3vILSKCeuXfiwDeTiwmviWxFEVFrfrICgGIxi8K7C11x_KLr8lscjQ4KIj9iu3iZMlY4k9qHVTG3rIJnTy8CRUfMOBVck.Z63ehHu2RN7wKH3u3BJYE33L8cnN2HH1no05XEDovtI&amp;dib_tag=se&amp;keywords=brass%2Bstandoffs%2Bm2*25&amp;qid=1764673038&amp;sprefix=brass%2Bstandoffs%2Bm2%2B25%2B%2Caps%2C1314&amp;sr=8-14&amp;th=1"/>
+    <hyperlink ref="B18" r:id="rId17" display="https://www.amazon.com/uxcell-Straight-Pillar-Standoff-M2x3x8mm/dp/B07H3SR8XX/ref=sr_1_1?crid=22GD2WBJM4T6R&amp;dib=eyJ2IjoiMSJ9.RgTnu8eTeo9HgMfjKSirbbzlrK7VUOMMW_Tetj9_uBW7YMSjjRYN9Kcs95xlV3Mf4G409qMg1_-41nx0ygYRGijhGsoqMlcaM8EwnuSb7uJjPp3oHmrzf0UEW4eIJ7xkFxObsAsFyK-DYkXwqtbtB8t_qVKVsS1lIMfR8WBf6DdpfPJ752u7cX2HQWjU6srcWXXm6cKo7RbB9d077hovpGkgmHpHh2KAjv0qd4rUeSI.1h2V5Zz6MWxfO_UFoV4SthSJYRHqemayKoiJ7oP25do&amp;dib_tag=se&amp;keywords=M2*8+brass+standoff&amp;qid=1764673852&amp;sprefix=m2+8+brass+standoff%2Caps%2C459&amp;sr=8-1"/>
+    <hyperlink ref="B19" r:id="rId18" display="https://www.amazon.com/uxcell-116pcs-Straight-Standoff-M2x3x3mm/dp/B07H3XJ7BB/ref=sr_1_2_sspa?crid=I18JF6N5XGV4&amp;dib=eyJ2IjoiMSJ9.gQrsJdjPio93kgEjHgW-4XW7Mb8U2JLjAC69J_OOVO_dAcQa__pK6mUT9LOFSV5YTOQWysEg_ydVKe_2R3pjHbgJDwWiqDDf-T2zb44YuyhQJpkrQPbclfVSmxHhjXr80am7RVGnmaPxitY5jHEPIVuh5PwPlOGg_57jkLg1zl51OAy9Z0N2datWjJdp4hZWKI6urnqAj5heKr7g1txqSK7wwKfh7-en2K4Rf2yoV3Y.Fs_COGMDQD-jL32D2JuKVAYtb3kO-2Y8HySBpIDGVpc&amp;dib_tag=se&amp;keywords=brass+standoff+M2+3*3&amp;qid=1764673961&amp;sprefix=brass+standoff+m2+3+3%2Caps%2C433&amp;sr=8-2-spons&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9hdGY&amp;psc=1"/>
+    <hyperlink ref="B20" r:id="rId19" display="https://www.amazon.com/Rubber-Assorted-Camping-Survival-Supplies/dp/B0BX4CYWB7/ref=sr_1_14?crid=B4AZ1YKM5D5N&amp;dib=eyJ2IjoiMSJ9.UFjdkXme7AA5dRx-2oC-AVCcSF6h5f7alhoxn5XH8GP1qJjO_ip9Aw1dg9oM8rN-9JIm5TMtKGnm5Tnr8Y9twSX5oy49r7DB724I9AfeqC1XQmwsxYtzAMG1ty05tDkJrTAA4QdAqHVN4f3QQs-Utg7FybPIGakgGtZeg1gWMC_mxeNiVAZIlLzwSaHSq5FXD44lks4X2RsTf1erGKGxl5USRk8Y4VoYn1fvQEtMyeOSKIkH-H-XHdR2Y0EFVIYD-Sd3y1j1ZYaRr5htTUyiBH5k9FM1WcEvu5Rtqq1KjdE.yeuMQysCZyUwRG4bb6f6EVyZOUDtI2ovu7416UOF3EE&amp;dib_tag=se&amp;keywords=wide%2Brubber%2Bband&amp;qid=1764674185&amp;sprefix=wide%2Brubber%2Bband%2Caps%2C512&amp;sr=8-14&amp;th=1"/>
+    <hyperlink ref="B22" r:id="rId20" display="https://www.amazon.com/Pre-Crimped-Connectors-SPRacingF3-Omnibus-Silicone/dp/B07PDQKHJ2/ref=sr_1_2?crid=121FJ5WRAUDJV&amp;dib=eyJ2IjoiMSJ9.Mnmg9cJrrWFJvQ5a9TnUEjeZq6mS-Ppv5D0VMbDcFgC5PWeQUxEoH7dDX_tcKBx6jxLpt2yJEGCdxxtbjjpDZIwSEeofSTFeC66scCsLB8T4NzElfFzcderHntyx6Sb758XlI0Wrbb5snUzVpNV75RuGnzJqck8mGYdP-5ZvZCp0O9TDs2BvAX4cauMaQtFI7NxAQp-pIuOALg5_KcUaEjL82f17JBGMyj5jPRmOzzDAoLFouiJuDZVIRmq1_K79zrNPgbLwZOSONPG_39uVcbqvwkjaH9ez8jRdOJYkKcQ.AuraxtE6zJgiz2mePhsDVmTAU0tI1S59LBRjLdJkzNE&amp;dib_tag=se&amp;keywords=sh1.0+4P&amp;qid=1764673453&amp;sprefix=sh1.0+4p%2Caps%2C385&amp;sr=8-2"/>
+    <hyperlink ref="B23" r:id="rId21" display="https://www.amazon.com/HFHYDZSW-MX1-25-1-25mm-Connector-Head_10PCS_7P/dp/B0DSTVJBH2/ref=sr_1_4?crid=3U38PMH42H40L&amp;dib=eyJ2IjoiMSJ9.iQPI25cX4s0cJQ-KKO3sbxDCPfzyTlmPY6yGcBhnFxXyY2ImqB6ebMRGZGWBMFnkx92qitPXGUBs2A9-icKYKCSodUz4Q7BYMGF7lF3gUhBVnSqBTbt0H4tTHoG4sof4HzhqF9dzda6khevIbzhgOlYhHZIIjDSGREtUcBwyQWAUIpRm02gc48Ij5S3UaiQw.a7yQE7_4qJOBz5dgtPrYDdicixtD-A1VVlTbosZk_GI&amp;dib_tag=se&amp;keywords=MX1.25%2B7p&amp;qid=1764673631&amp;sprefix=mx1.25%2B7p%2Caps%2C372&amp;sr=8-4&amp;th=1"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
